--- a/testdata/configurationTST/execute.xlsx
+++ b/testdata/configurationTST/execute.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13560" windowHeight="5976"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$165</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="342">
   <si>
     <t>App</t>
   </si>
@@ -81,6 +81,9 @@
     <t>C70780</t>
   </si>
   <si>
+    <t>off</t>
+  </si>
+  <si>
     <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
   </si>
   <si>
@@ -843,7 +846,7 @@
     <t>C70908</t>
   </si>
   <si>
-    <t>General-Login_Page_Elements-Overview_Info_Page_[MOB_ANDROID]</t>
+    <t>Mobile_Login-Generate_OTP-Inside_30_Seconds_[MOB_ANDROID]</t>
   </si>
   <si>
     <t>C70909</t>
@@ -873,12 +876,6 @@
     <t>C70913</t>
   </si>
   <si>
-    <t>5,</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Purpose_Code_289_invalid</t>
   </si>
   <si>
@@ -957,10 +954,109 @@
     <t>C70926</t>
   </si>
   <si>
+    <t>C70927</t>
+  </si>
+  <si>
+    <t>C70928</t>
+  </si>
+  <si>
+    <t>C70929</t>
+  </si>
+  <si>
+    <t>C70930</t>
+  </si>
+  <si>
+    <t>C70931</t>
+  </si>
+  <si>
+    <t>C70932</t>
+  </si>
+  <si>
+    <t>C70933</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70934</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Card_[ANDROID]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70935</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Card_[ANDROID]-From_Saving_Account</t>
+  </si>
+  <si>
+    <t>C70936</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[ANDROID]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70937</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[ANDROID]-From_Saving_Account</t>
+  </si>
+  <si>
+    <t>C70938</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[ANDROID]-Internal_Transfer</t>
+  </si>
+  <si>
+    <t>C70939</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[ANDROID]-Domestic_Payment</t>
+  </si>
+  <si>
+    <t>C70940</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[ANDROID]-Prenesi</t>
+  </si>
+  <si>
+    <t>C70941</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Transaction_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70942</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[MOB_ANDROID]-View_And_Repeat</t>
+  </si>
+  <si>
+    <t>C70943</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]-To_Current_Authorized_Account</t>
+  </si>
+  <si>
+    <t>C70944</t>
+  </si>
+  <si>
     <t>Automated Test Names</t>
   </si>
   <si>
-    <t>Mobile_Login-Generate_OTP-Inside_30_Seconds_[MOB_ANDROID]</t>
+    <t>Payments_Own_Account_Transfer_To_Loan_[ANDROID]</t>
+  </si>
+  <si>
+    <t>Not Automated</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>Manage_Products_Nickname_Product_[MOB_ANDROID]</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1452,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1405,6 +1501,43 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1529,7 +1662,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1541,34 +1674,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1653,7 +1786,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1671,11 +1804,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2014,7 +2151,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
@@ -2063,7 +2200,7 @@
       <c r="F2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2086,8 +2223,8 @@
       <c r="F3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>13</v>
+      <c r="G3" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:7">
@@ -2095,10 +2232,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>10</v>
@@ -2109,7 +2246,7 @@
       <c r="F4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2117,11 +2254,11 @@
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>18</v>
+      <c r="B5" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>10</v>
@@ -2132,19 +2269,19 @@
       <c r="F5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>13</v>
+      <c r="G5" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>20</v>
+      <c r="B6" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>10</v>
@@ -2155,19 +2292,19 @@
       <c r="F6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>13</v>
+      <c r="G6" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>22</v>
+      <c r="B7" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>10</v>
@@ -2178,19 +2315,19 @@
       <c r="F7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>13</v>
+      <c r="G7" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>24</v>
+      <c r="B8" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>10</v>
@@ -2201,19 +2338,19 @@
       <c r="F8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>13</v>
+      <c r="G8" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:7">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>26</v>
+      <c r="B9" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>10</v>
@@ -2224,19 +2361,19 @@
       <c r="F9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>13</v>
+      <c r="G9" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:7">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>28</v>
+      <c r="B10" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>10</v>
@@ -2247,19 +2384,19 @@
       <c r="F10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>13</v>
+      <c r="G10" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:7">
       <c r="A11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>30</v>
+      <c r="B11" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>10</v>
@@ -2270,19 +2407,19 @@
       <c r="F11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>13</v>
+      <c r="G11" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:7">
       <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>32</v>
+      <c r="B12" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>10</v>
@@ -2293,19 +2430,19 @@
       <c r="F12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>13</v>
+      <c r="G12" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:7">
       <c r="A13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>34</v>
+      <c r="B13" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>10</v>
@@ -2316,19 +2453,19 @@
       <c r="F13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>13</v>
+      <c r="G13" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:7">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>36</v>
+      <c r="B14" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>10</v>
@@ -2339,8 +2476,8 @@
       <c r="F14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="9" t="s">
-        <v>13</v>
+      <c r="G14" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:7">
@@ -2348,10 +2485,10 @@
         <v>7</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>10</v>
@@ -2362,8 +2499,8 @@
       <c r="F15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>13</v>
+      <c r="G15" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:7">
@@ -2371,10 +2508,10 @@
         <v>7</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>10</v>
@@ -2385,8 +2522,8 @@
       <c r="F16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>13</v>
+      <c r="G16" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:7">
@@ -2394,10 +2531,10 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>10</v>
@@ -2408,8 +2545,8 @@
       <c r="F17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="9" t="s">
-        <v>13</v>
+      <c r="G17" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:7">
@@ -2417,10 +2554,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>10</v>
@@ -2431,8 +2568,8 @@
       <c r="F18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>13</v>
+      <c r="G18" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:7">
@@ -2440,10 +2577,10 @@
         <v>7</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>10</v>
@@ -2454,8 +2591,8 @@
       <c r="F19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="9" t="s">
-        <v>13</v>
+      <c r="G19" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:7">
@@ -2463,10 +2600,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>10</v>
@@ -2477,8 +2614,8 @@
       <c r="F20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>13</v>
+      <c r="G20" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:7">
@@ -2486,10 +2623,10 @@
         <v>7</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>10</v>
@@ -2500,8 +2637,8 @@
       <c r="F21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="9" t="s">
-        <v>13</v>
+      <c r="G21" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:7">
@@ -2509,10 +2646,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>10</v>
@@ -2523,8 +2660,8 @@
       <c r="F22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="9" t="s">
-        <v>13</v>
+      <c r="G22" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:7">
@@ -2532,10 +2669,10 @@
         <v>7</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>10</v>
@@ -2546,8 +2683,8 @@
       <c r="F23" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="9" t="s">
-        <v>13</v>
+      <c r="G23" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:7">
@@ -2555,10 +2692,10 @@
         <v>7</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>10</v>
@@ -2569,8 +2706,8 @@
       <c r="F24" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="9" t="s">
-        <v>13</v>
+      <c r="G24" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:7">
@@ -2578,10 +2715,10 @@
         <v>7</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>10</v>
@@ -2592,8 +2729,8 @@
       <c r="F25" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="9" t="s">
-        <v>13</v>
+      <c r="G25" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:7">
@@ -2601,10 +2738,10 @@
         <v>7</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>10</v>
@@ -2615,8 +2752,8 @@
       <c r="F26" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="9" t="s">
-        <v>13</v>
+      <c r="G26" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:7">
@@ -2624,10 +2761,10 @@
         <v>7</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>10</v>
@@ -2638,8 +2775,8 @@
       <c r="F27" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="9" t="s">
-        <v>13</v>
+      <c r="G27" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:7">
@@ -2647,10 +2784,10 @@
         <v>7</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>10</v>
@@ -2661,8 +2798,8 @@
       <c r="F28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="9" t="s">
-        <v>13</v>
+      <c r="G28" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:7">
@@ -2670,10 +2807,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>10</v>
@@ -2684,8 +2821,8 @@
       <c r="F29" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="9" t="s">
-        <v>13</v>
+      <c r="G29" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:7">
@@ -2693,10 +2830,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>10</v>
@@ -2707,8 +2844,8 @@
       <c r="F30" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="9" t="s">
-        <v>13</v>
+      <c r="G30" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:7">
@@ -2716,10 +2853,10 @@
         <v>7</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>10</v>
@@ -2730,8 +2867,8 @@
       <c r="F31" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="9" t="s">
-        <v>13</v>
+      <c r="G31" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:7">
@@ -2739,10 +2876,10 @@
         <v>7</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>10</v>
@@ -2753,8 +2890,8 @@
       <c r="F32" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="9" t="s">
-        <v>13</v>
+      <c r="G32" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:7">
@@ -2762,10 +2899,10 @@
         <v>7</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>10</v>
@@ -2776,7 +2913,7 @@
       <c r="F33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2784,11 +2921,11 @@
       <c r="A34" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>76</v>
+      <c r="B34" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>10</v>
@@ -2799,19 +2936,19 @@
       <c r="F34" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>13</v>
+      <c r="G34" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:7">
       <c r="A35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>78</v>
+      <c r="B35" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>10</v>
@@ -2822,7 +2959,7 @@
       <c r="F35" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2830,11 +2967,11 @@
       <c r="A36" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>80</v>
+      <c r="B36" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>10</v>
@@ -2845,8 +2982,8 @@
       <c r="F36" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="9" t="s">
-        <v>13</v>
+      <c r="G36" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:7">
@@ -2854,10 +2991,10 @@
         <v>7</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>10</v>
@@ -2868,8 +3005,8 @@
       <c r="F37" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="9" t="s">
-        <v>13</v>
+      <c r="G37" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:7">
@@ -2877,10 +3014,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>10</v>
@@ -2891,7 +3028,7 @@
       <c r="F38" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2900,10 +3037,10 @@
         <v>7</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>10</v>
@@ -2914,8 +3051,8 @@
       <c r="F39" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="9" t="s">
-        <v>13</v>
+      <c r="G39" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:7">
@@ -2923,10 +3060,10 @@
         <v>7</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>10</v>
@@ -2937,7 +3074,7 @@
       <c r="F40" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2945,11 +3082,11 @@
       <c r="A41" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>90</v>
+      <c r="B41" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>10</v>
@@ -2960,19 +3097,19 @@
       <c r="F41" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="9" t="s">
-        <v>13</v>
+      <c r="G41" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
       <c r="A42" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>92</v>
+      <c r="B42" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>10</v>
@@ -2983,19 +3120,19 @@
       <c r="F42" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="9" t="s">
-        <v>13</v>
+      <c r="G42" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:7">
       <c r="A43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>94</v>
+      <c r="B43" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>10</v>
@@ -3006,8 +3143,8 @@
       <c r="F43" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="9" t="s">
-        <v>13</v>
+      <c r="G43" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:7">
@@ -3015,10 +3152,10 @@
         <v>7</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>10</v>
@@ -3029,8 +3166,8 @@
       <c r="F44" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="9" t="s">
-        <v>13</v>
+      <c r="G44" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:7">
@@ -3038,10 +3175,10 @@
         <v>7</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>10</v>
@@ -3052,8 +3189,8 @@
       <c r="F45" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="9" t="s">
-        <v>13</v>
+      <c r="G45" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:7">
@@ -3061,10 +3198,10 @@
         <v>7</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>10</v>
@@ -3075,8 +3212,8 @@
       <c r="F46" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="9" t="s">
-        <v>13</v>
+      <c r="G46" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:7">
@@ -3084,10 +3221,10 @@
         <v>7</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>10</v>
@@ -3098,7 +3235,7 @@
       <c r="F47" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3107,10 +3244,10 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>10</v>
@@ -3121,8 +3258,8 @@
       <c r="F48" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="9" t="s">
-        <v>13</v>
+      <c r="G48" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:7">
@@ -3130,10 +3267,10 @@
         <v>7</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>10</v>
@@ -3144,8 +3281,8 @@
       <c r="F49" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="9" t="s">
-        <v>13</v>
+      <c r="G49" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:7">
@@ -3153,10 +3290,10 @@
         <v>7</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>10</v>
@@ -3167,8 +3304,8 @@
       <c r="F50" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="9" t="s">
-        <v>13</v>
+      <c r="G50" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:7">
@@ -3176,10 +3313,10 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>10</v>
@@ -3190,7 +3327,7 @@
       <c r="F51" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3199,10 +3336,10 @@
         <v>7</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>10</v>
@@ -3213,8 +3350,8 @@
       <c r="F52" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="9" t="s">
-        <v>13</v>
+      <c r="G52" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:7">
@@ -3222,10 +3359,10 @@
         <v>7</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>10</v>
@@ -3236,8 +3373,8 @@
       <c r="F53" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="9" t="s">
-        <v>13</v>
+      <c r="G53" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -3245,10 +3382,10 @@
         <v>7</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>10</v>
@@ -3259,8 +3396,8 @@
       <c r="F54" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G54" s="9" t="s">
-        <v>13</v>
+      <c r="G54" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -3268,10 +3405,10 @@
         <v>7</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>10</v>
@@ -3282,8 +3419,8 @@
       <c r="F55" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="9" t="s">
-        <v>13</v>
+      <c r="G55" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:7">
@@ -3291,10 +3428,10 @@
         <v>7</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>10</v>
@@ -3305,7 +3442,7 @@
       <c r="F56" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3314,10 +3451,10 @@
         <v>7</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>10</v>
@@ -3328,8 +3465,8 @@
       <c r="F57" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="9" t="s">
-        <v>13</v>
+      <c r="G57" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:7">
@@ -3337,10 +3474,10 @@
         <v>7</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>10</v>
@@ -3351,8 +3488,8 @@
       <c r="F58" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="9" t="s">
-        <v>13</v>
+      <c r="G58" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:7">
@@ -3360,10 +3497,10 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>10</v>
@@ -3374,8 +3511,8 @@
       <c r="F59" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G59" s="9" t="s">
-        <v>13</v>
+      <c r="G59" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -3383,10 +3520,10 @@
         <v>7</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>10</v>
@@ -3397,8 +3534,8 @@
       <c r="F60" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="9" t="s">
-        <v>13</v>
+      <c r="G60" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:7">
@@ -3406,10 +3543,10 @@
         <v>7</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>10</v>
@@ -3420,8 +3557,8 @@
       <c r="F61" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G61" s="9" t="s">
-        <v>13</v>
+      <c r="G61" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:7">
@@ -3429,10 +3566,10 @@
         <v>7</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>10</v>
@@ -3443,8 +3580,8 @@
       <c r="F62" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="9" t="s">
-        <v>13</v>
+      <c r="G62" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:7">
@@ -3452,10 +3589,10 @@
         <v>7</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>10</v>
@@ -3466,8 +3603,8 @@
       <c r="F63" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="9" t="s">
-        <v>13</v>
+      <c r="G63" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:7">
@@ -3475,10 +3612,10 @@
         <v>7</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>10</v>
@@ -3489,8 +3626,8 @@
       <c r="F64" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G64" s="9" t="s">
-        <v>13</v>
+      <c r="G64" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:7">
@@ -3498,10 +3635,10 @@
         <v>7</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>10</v>
@@ -3512,8 +3649,8 @@
       <c r="F65" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="9" t="s">
-        <v>13</v>
+      <c r="G65" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:7">
@@ -3521,10 +3658,10 @@
         <v>7</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>10</v>
@@ -3535,8 +3672,8 @@
       <c r="F66" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="9" t="s">
-        <v>13</v>
+      <c r="G66" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:7">
@@ -3544,10 +3681,10 @@
         <v>7</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>10</v>
@@ -3558,8 +3695,8 @@
       <c r="F67" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G67" s="9" t="s">
-        <v>13</v>
+      <c r="G67" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:7">
@@ -3567,10 +3704,10 @@
         <v>7</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>10</v>
@@ -3581,8 +3718,8 @@
       <c r="F68" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="9" t="s">
-        <v>13</v>
+      <c r="G68" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:7">
@@ -3590,10 +3727,10 @@
         <v>7</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>10</v>
@@ -3604,8 +3741,8 @@
       <c r="F69" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G69" s="9" t="s">
-        <v>13</v>
+      <c r="G69" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -3613,10 +3750,10 @@
         <v>7</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>10</v>
@@ -3627,8 +3764,8 @@
       <c r="F70" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="9" t="s">
-        <v>13</v>
+      <c r="G70" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:7">
@@ -3636,10 +3773,10 @@
         <v>7</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>10</v>
@@ -3650,7 +3787,7 @@
       <c r="F71" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G71" s="9" t="s">
+      <c r="G71" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3659,10 +3796,10 @@
         <v>7</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>10</v>
@@ -3673,7 +3810,7 @@
       <c r="F72" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="9" t="s">
+      <c r="G72" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3682,10 +3819,10 @@
         <v>7</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>10</v>
@@ -3696,8 +3833,8 @@
       <c r="F73" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="9" t="s">
-        <v>13</v>
+      <c r="G73" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:7">
@@ -3705,10 +3842,10 @@
         <v>7</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>10</v>
@@ -3719,8 +3856,8 @@
       <c r="F74" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G74" s="9" t="s">
-        <v>13</v>
+      <c r="G74" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:7">
@@ -3728,10 +3865,10 @@
         <v>7</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>10</v>
@@ -3742,8 +3879,8 @@
       <c r="F75" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="9" t="s">
-        <v>13</v>
+      <c r="G75" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:7">
@@ -3751,10 +3888,10 @@
         <v>7</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>10</v>
@@ -3765,8 +3902,8 @@
       <c r="F76" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="9" t="s">
-        <v>13</v>
+      <c r="G76" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:7">
@@ -3774,10 +3911,10 @@
         <v>7</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>10</v>
@@ -3788,8 +3925,8 @@
       <c r="F77" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G77" s="9" t="s">
-        <v>13</v>
+      <c r="G77" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:7">
@@ -3797,10 +3934,10 @@
         <v>7</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>10</v>
@@ -3811,7 +3948,7 @@
       <c r="F78" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="9" t="s">
+      <c r="G78" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3820,10 +3957,10 @@
         <v>7</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>10</v>
@@ -3834,8 +3971,8 @@
       <c r="F79" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G79" s="9" t="s">
-        <v>13</v>
+      <c r="G79" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:7">
@@ -3843,10 +3980,10 @@
         <v>7</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>10</v>
@@ -3857,7 +3994,7 @@
       <c r="F80" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="9" t="s">
+      <c r="G80" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3866,10 +4003,10 @@
         <v>7</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>10</v>
@@ -3880,8 +4017,8 @@
       <c r="F81" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G81" s="9" t="s">
-        <v>13</v>
+      <c r="G81" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:7">
@@ -3889,10 +4026,10 @@
         <v>7</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>10</v>
@@ -3903,8 +4040,8 @@
       <c r="F82" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="9" t="s">
-        <v>13</v>
+      <c r="G82" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -3912,10 +4049,10 @@
         <v>7</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>10</v>
@@ -3926,8 +4063,8 @@
       <c r="F83" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G83" s="9" t="s">
-        <v>13</v>
+      <c r="G83" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -3935,10 +4072,10 @@
         <v>7</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>10</v>
@@ -3949,8 +4086,8 @@
       <c r="F84" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G84" s="9" t="s">
-        <v>13</v>
+      <c r="G84" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:7">
@@ -3958,10 +4095,10 @@
         <v>7</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>10</v>
@@ -3972,7 +4109,7 @@
       <c r="F85" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G85" s="9" t="s">
+      <c r="G85" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3981,10 +4118,10 @@
         <v>7</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>10</v>
@@ -3995,8 +4132,8 @@
       <c r="F86" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G86" s="9" t="s">
-        <v>13</v>
+      <c r="G86" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:7">
@@ -4004,10 +4141,10 @@
         <v>7</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>10</v>
@@ -4018,7 +4155,7 @@
       <c r="F87" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G87" s="9" t="s">
+      <c r="G87" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4027,10 +4164,10 @@
         <v>7</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>10</v>
@@ -4041,8 +4178,8 @@
       <c r="F88" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="9" t="s">
-        <v>13</v>
+      <c r="G88" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:7">
@@ -4050,10 +4187,10 @@
         <v>7</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>10</v>
@@ -4064,8 +4201,8 @@
       <c r="F89" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="9" t="s">
-        <v>13</v>
+      <c r="G89" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:7">
@@ -4073,10 +4210,10 @@
         <v>7</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>10</v>
@@ -4087,8 +4224,8 @@
       <c r="F90" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G90" s="9" t="s">
-        <v>13</v>
+      <c r="G90" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:7">
@@ -4096,10 +4233,10 @@
         <v>7</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>10</v>
@@ -4110,7 +4247,7 @@
       <c r="F91" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G91" s="9" t="s">
+      <c r="G91" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4119,10 +4256,10 @@
         <v>7</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>10</v>
@@ -4133,7 +4270,7 @@
       <c r="F92" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G92" s="9" t="s">
+      <c r="G92" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4142,10 +4279,10 @@
         <v>7</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>10</v>
@@ -4156,8 +4293,8 @@
       <c r="F93" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G93" s="9" t="s">
-        <v>13</v>
+      <c r="G93" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -4165,10 +4302,10 @@
         <v>7</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>10</v>
@@ -4179,8 +4316,8 @@
       <c r="F94" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G94" s="9" t="s">
-        <v>13</v>
+      <c r="G94" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:7">
@@ -4188,10 +4325,10 @@
         <v>7</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>10</v>
@@ -4202,8 +4339,8 @@
       <c r="F95" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G95" s="9" t="s">
-        <v>13</v>
+      <c r="G95" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:7">
@@ -4211,10 +4348,10 @@
         <v>7</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>10</v>
@@ -4225,8 +4362,8 @@
       <c r="F96" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G96" s="9" t="s">
-        <v>13</v>
+      <c r="G96" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:7">
@@ -4234,10 +4371,10 @@
         <v>7</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>10</v>
@@ -4248,8 +4385,8 @@
       <c r="F97" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G97" s="9" t="s">
-        <v>13</v>
+      <c r="G97" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:7">
@@ -4257,10 +4394,10 @@
         <v>7</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>10</v>
@@ -4271,7 +4408,7 @@
       <c r="F98" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G98" s="9" t="s">
+      <c r="G98" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4280,10 +4417,10 @@
         <v>7</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>10</v>
@@ -4294,8 +4431,8 @@
       <c r="F99" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="9" t="s">
-        <v>13</v>
+      <c r="G99" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:7">
@@ -4303,10 +4440,10 @@
         <v>7</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>10</v>
@@ -4317,7 +4454,7 @@
       <c r="F100" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G100" s="9" t="s">
+      <c r="G100" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4326,10 +4463,10 @@
         <v>7</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>10</v>
@@ -4340,8 +4477,8 @@
       <c r="F101" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G101" s="9" t="s">
-        <v>13</v>
+      <c r="G101" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:7">
@@ -4349,10 +4486,10 @@
         <v>7</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>10</v>
@@ -4363,8 +4500,8 @@
       <c r="F102" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="9" t="s">
-        <v>13</v>
+      <c r="G102" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:7">
@@ -4372,10 +4509,10 @@
         <v>7</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>10</v>
@@ -4386,8 +4523,8 @@
       <c r="F103" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G103" s="9" t="s">
-        <v>13</v>
+      <c r="G103" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:7">
@@ -4395,10 +4532,10 @@
         <v>7</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>10</v>
@@ -4409,8 +4546,8 @@
       <c r="F104" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G104" s="9" t="s">
-        <v>13</v>
+      <c r="G104" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -4418,10 +4555,10 @@
         <v>7</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>10</v>
@@ -4432,8 +4569,8 @@
       <c r="F105" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G105" s="9" t="s">
-        <v>13</v>
+      <c r="G105" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:7">
@@ -4441,10 +4578,10 @@
         <v>7</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>10</v>
@@ -4455,8 +4592,8 @@
       <c r="F106" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G106" s="9" t="s">
-        <v>13</v>
+      <c r="G106" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:7">
@@ -4464,10 +4601,10 @@
         <v>7</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>10</v>
@@ -4478,8 +4615,8 @@
       <c r="F107" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G107" s="9" t="s">
-        <v>13</v>
+      <c r="G107" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:7">
@@ -4487,10 +4624,10 @@
         <v>7</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>10</v>
@@ -4501,8 +4638,8 @@
       <c r="F108" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G108" s="9" t="s">
-        <v>13</v>
+      <c r="G108" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:7">
@@ -4510,10 +4647,10 @@
         <v>7</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>10</v>
@@ -4524,7 +4661,7 @@
       <c r="F109" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G109" s="9" t="s">
+      <c r="G109" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4533,10 +4670,10 @@
         <v>7</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>10</v>
@@ -4547,8 +4684,8 @@
       <c r="F110" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G110" s="9" t="s">
-        <v>13</v>
+      <c r="G110" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:7">
@@ -4556,10 +4693,10 @@
         <v>7</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>10</v>
@@ -4570,7 +4707,7 @@
       <c r="F111" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G111" s="9" t="s">
+      <c r="G111" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4579,10 +4716,10 @@
         <v>7</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>10</v>
@@ -4593,7 +4730,7 @@
       <c r="F112" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G112" s="9" t="s">
+      <c r="G112" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4602,10 +4739,10 @@
         <v>7</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>10</v>
@@ -4616,7 +4753,7 @@
       <c r="F113" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G113" s="9" t="s">
+      <c r="G113" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4625,10 +4762,10 @@
         <v>7</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>10</v>
@@ -4639,7 +4776,7 @@
       <c r="F114" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G114" s="9" t="s">
+      <c r="G114" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4648,10 +4785,10 @@
         <v>7</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>10</v>
@@ -4662,7 +4799,7 @@
       <c r="F115" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="9" t="s">
+      <c r="G115" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4671,10 +4808,10 @@
         <v>7</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>10</v>
@@ -4685,7 +4822,7 @@
       <c r="F116" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G116" s="9" t="s">
+      <c r="G116" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4694,10 +4831,10 @@
         <v>7</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>10</v>
@@ -4708,7 +4845,7 @@
       <c r="F117" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G117" s="9" t="s">
+      <c r="G117" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4717,10 +4854,10 @@
         <v>7</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>10</v>
@@ -4731,7 +4868,7 @@
       <c r="F118" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G118" s="9" t="s">
+      <c r="G118" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4740,10 +4877,10 @@
         <v>7</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>10</v>
@@ -4754,7 +4891,7 @@
       <c r="F119" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G119" s="9" t="s">
+      <c r="G119" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4763,10 +4900,10 @@
         <v>7</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>10</v>
@@ -4777,8 +4914,8 @@
       <c r="F120" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G120" s="9" t="s">
-        <v>13</v>
+      <c r="G120" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:7">
@@ -4786,10 +4923,10 @@
         <v>7</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>10</v>
@@ -4800,8 +4937,8 @@
       <c r="F121" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G121" s="9" t="s">
-        <v>13</v>
+      <c r="G121" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:7">
@@ -4809,10 +4946,10 @@
         <v>7</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>10</v>
@@ -4823,7 +4960,7 @@
       <c r="F122" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G122" s="9" t="s">
+      <c r="G122" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4832,10 +4969,10 @@
         <v>7</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>10</v>
@@ -4846,7 +4983,7 @@
       <c r="F123" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G123" s="9" t="s">
+      <c r="G123" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4855,10 +4992,10 @@
         <v>7</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>10</v>
@@ -4869,7 +5006,7 @@
       <c r="F124" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G124" s="9" t="s">
+      <c r="G124" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4878,10 +5015,10 @@
         <v>7</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>10</v>
@@ -4892,7 +5029,7 @@
       <c r="F125" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G125" s="9" t="s">
+      <c r="G125" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4901,10 +5038,10 @@
         <v>7</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>10</v>
@@ -4915,8 +5052,8 @@
       <c r="F126" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G126" s="9" t="s">
-        <v>13</v>
+      <c r="G126" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -4924,10 +5061,10 @@
         <v>7</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>10</v>
@@ -4938,7 +5075,7 @@
       <c r="F127" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G127" s="9" t="s">
+      <c r="G127" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4947,10 +5084,10 @@
         <v>7</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>10</v>
@@ -4961,7 +5098,7 @@
       <c r="F128" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="9" t="s">
+      <c r="G128" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4970,10 +5107,10 @@
         <v>7</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>10</v>
@@ -4984,7 +5121,7 @@
       <c r="F129" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G129" s="9" t="s">
+      <c r="G129" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4993,10 +5130,10 @@
         <v>7</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>10</v>
@@ -5007,7 +5144,7 @@
       <c r="F130" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G130" s="9" t="s">
+      <c r="G130" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5016,10 +5153,10 @@
         <v>7</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>10</v>
@@ -5030,7 +5167,7 @@
       <c r="F131" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G131" s="9" t="s">
+      <c r="G131" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5039,10 +5176,10 @@
         <v>7</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>10</v>
@@ -5053,7 +5190,7 @@
       <c r="F132" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G132" s="9" t="s">
+      <c r="G132" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5062,10 +5199,10 @@
         <v>7</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>10</v>
@@ -5076,7 +5213,7 @@
       <c r="F133" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G133" s="9" t="s">
+      <c r="G133" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5085,10 +5222,10 @@
         <v>7</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>10</v>
@@ -5099,7 +5236,7 @@
       <c r="F134" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G134" s="9" t="s">
+      <c r="G134" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5108,21 +5245,21 @@
         <v>7</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>280</v>
+        <v>10</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>281</v>
+        <v>11</v>
       </c>
       <c r="F135" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G135" s="9" t="s">
+      <c r="G135" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5131,11 +5268,11 @@
         <v>7</v>
       </c>
       <c r="B136" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C136" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>283</v>
-      </c>
       <c r="D136" s="6" t="s">
         <v>10</v>
       </c>
@@ -5145,7 +5282,7 @@
       <c r="F136" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G136" s="9" t="s">
+      <c r="G136" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5154,11 +5291,11 @@
         <v>7</v>
       </c>
       <c r="B137" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>285</v>
-      </c>
       <c r="D137" s="6" t="s">
         <v>10</v>
       </c>
@@ -5168,7 +5305,7 @@
       <c r="F137" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G137" s="9" t="s">
+      <c r="G137" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5177,11 +5314,11 @@
         <v>7</v>
       </c>
       <c r="B138" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>287</v>
-      </c>
       <c r="D138" s="6" t="s">
         <v>10</v>
       </c>
@@ -5191,7 +5328,7 @@
       <c r="F138" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G138" s="9" t="s">
+      <c r="G138" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5200,11 +5337,11 @@
         <v>7</v>
       </c>
       <c r="B139" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C139" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>289</v>
-      </c>
       <c r="D139" s="6" t="s">
         <v>10</v>
       </c>
@@ -5214,7 +5351,7 @@
       <c r="F139" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G139" s="9" t="s">
+      <c r="G139" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5223,11 +5360,11 @@
         <v>7</v>
       </c>
       <c r="B140" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C140" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>291</v>
-      </c>
       <c r="D140" s="6" t="s">
         <v>10</v>
       </c>
@@ -5237,7 +5374,7 @@
       <c r="F140" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G140" s="9" t="s">
+      <c r="G140" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5246,11 +5383,11 @@
         <v>7</v>
       </c>
       <c r="B141" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="D141" s="6" t="s">
         <v>10</v>
       </c>
@@ -5260,7 +5397,7 @@
       <c r="F141" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G141" s="9" t="s">
+      <c r="G141" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5269,11 +5406,11 @@
         <v>7</v>
       </c>
       <c r="B142" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>295</v>
-      </c>
       <c r="D142" s="6" t="s">
         <v>10</v>
       </c>
@@ -5283,7 +5420,7 @@
       <c r="F142" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G142" s="9" t="s">
+      <c r="G142" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5292,11 +5429,11 @@
         <v>7</v>
       </c>
       <c r="B143" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>297</v>
-      </c>
       <c r="D143" s="6" t="s">
         <v>10</v>
       </c>
@@ -5306,7 +5443,7 @@
       <c r="F143" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G143" s="9" t="s">
+      <c r="G143" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5315,11 +5452,11 @@
         <v>7</v>
       </c>
       <c r="B144" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>299</v>
-      </c>
       <c r="D144" s="6" t="s">
         <v>10</v>
       </c>
@@ -5329,7 +5466,7 @@
       <c r="F144" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G144" s="9" t="s">
+      <c r="G144" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5338,11 +5475,11 @@
         <v>7</v>
       </c>
       <c r="B145" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C145" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>301</v>
-      </c>
       <c r="D145" s="6" t="s">
         <v>10</v>
       </c>
@@ -5352,7 +5489,7 @@
       <c r="F145" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G145" s="9" t="s">
+      <c r="G145" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5361,11 +5498,11 @@
         <v>7</v>
       </c>
       <c r="B146" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>303</v>
-      </c>
       <c r="D146" s="6" t="s">
         <v>10</v>
       </c>
@@ -5375,7 +5512,7 @@
       <c r="F146" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G146" s="9" t="s">
+      <c r="G146" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5384,11 +5521,11 @@
         <v>7</v>
       </c>
       <c r="B147" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C147" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>305</v>
-      </c>
       <c r="D147" s="6" t="s">
         <v>10</v>
       </c>
@@ -5398,7 +5535,7 @@
       <c r="F147" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G147" s="9" t="s">
+      <c r="G147" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5406,235 +5543,747 @@
       <c r="A148" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B148" s="11" t="s">
+      <c r="B148" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C148" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="D148" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" spans="1:7">
+      <c r="A149" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C149" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="D148" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F148" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G148" s="9" t="s">
+      <c r="D149" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G149" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="149" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A149" s="6"/>
-      <c r="B149" s="3"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="8"/>
-    </row>
-    <row r="150" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A150" s="6"/>
-      <c r="B150" s="3"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="8"/>
-    </row>
-    <row r="151" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A151" s="6"/>
-      <c r="B151" s="3"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="8"/>
-    </row>
-    <row r="152" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A152" s="6"/>
-      <c r="B152" s="3"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="8"/>
-    </row>
-    <row r="153" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A153" s="6"/>
-      <c r="B153" s="3"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="8"/>
-    </row>
-    <row r="154" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A154" s="6"/>
-      <c r="B154" s="3"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="8"/>
-    </row>
-    <row r="155" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A155" s="6"/>
-      <c r="B155" s="3"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="8"/>
-    </row>
-    <row r="156" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A156" s="6"/>
-      <c r="B156" s="3"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="8"/>
-    </row>
-    <row r="157" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A157" s="6"/>
-      <c r="B157" s="3"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="8"/>
-    </row>
-    <row r="158" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A158" s="6"/>
-      <c r="B158" s="3"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="8"/>
-    </row>
-    <row r="159" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A159" s="6"/>
-      <c r="B159" s="3"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="8"/>
-    </row>
-    <row r="160" customFormat="1" ht="15.15" spans="1:7">
-      <c r="A160" s="6"/>
-      <c r="B160" s="3"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="6"/>
-      <c r="F160" s="8"/>
-    </row>
-    <row r="161" customFormat="1" ht="15.15" spans="1:6">
-      <c r="A161" s="6"/>
-      <c r="B161" s="3"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="8"/>
-    </row>
-    <row r="162" customFormat="1" ht="15.15" spans="1:6">
-      <c r="A162" s="6"/>
-      <c r="B162" s="3"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="6"/>
-      <c r="F162" s="8"/>
-    </row>
-    <row r="163" ht="15.15" spans="1:6">
-      <c r="B163" s="3"/>
-    </row>
-    <row r="164" ht="15.15" spans="1:6">
-      <c r="B164" s="3"/>
-    </row>
-    <row r="165" ht="15.15" spans="1:6">
-      <c r="B165" s="3"/>
-    </row>
-    <row r="166" ht="15.15" spans="1:6">
-      <c r="B166" s="3"/>
-    </row>
-    <row r="167" ht="15.15" spans="1:6">
-      <c r="B167" s="3"/>
-    </row>
-    <row r="168" ht="15.15" spans="1:6">
-      <c r="B168" s="3"/>
-    </row>
-    <row r="169" ht="15.15" spans="1:6">
-      <c r="B169" s="3"/>
-    </row>
-    <row r="170" ht="15.15" spans="1:6">
-      <c r="B170" s="3"/>
-    </row>
-    <row r="171" ht="15.15" spans="1:6">
-      <c r="B171" s="3"/>
-    </row>
-    <row r="172" ht="15.15" spans="1:6">
-      <c r="B172" s="3"/>
-    </row>
-    <row r="173" ht="15.15" spans="1:6">
-      <c r="B173" s="3"/>
-    </row>
-    <row r="174" ht="15.15" spans="1:6">
-      <c r="B174" s="3"/>
-    </row>
-    <row r="175" ht="15.15" spans="1:6">
-      <c r="B175" s="3"/>
-    </row>
-    <row r="176" ht="15.15" spans="1:6">
-      <c r="B176" s="3"/>
-    </row>
-    <row r="177" ht="15.15" spans="2:2">
-      <c r="B177" s="3"/>
-    </row>
-    <row r="178" ht="15.15" spans="2:2">
-      <c r="B178" s="3"/>
-    </row>
-    <row r="179" ht="15.15" spans="2:2">
-      <c r="B179" s="3"/>
-    </row>
-    <row r="180" ht="15.15" spans="2:2">
-      <c r="B180" s="3"/>
-    </row>
-    <row r="181" ht="15.15" spans="2:2">
-      <c r="B181" s="3"/>
-    </row>
-    <row r="182" ht="15.15" spans="2:2">
-      <c r="B182" s="3"/>
-    </row>
-    <row r="183" ht="15.15" spans="2:2">
-      <c r="B183" s="3"/>
-    </row>
-    <row r="184" ht="15.15" spans="2:2">
-      <c r="B184" s="3"/>
-    </row>
-    <row r="185" ht="15.15" spans="2:2">
-      <c r="B185" s="3"/>
-    </row>
-    <row r="186" ht="15.15" spans="2:2">
-      <c r="B186" s="3"/>
-    </row>
-    <row r="187" ht="15.15" spans="2:2">
-      <c r="B187" s="3"/>
-    </row>
-    <row r="188" ht="15.15" spans="2:2">
-      <c r="B188" s="3"/>
-    </row>
-    <row r="189" ht="15.15" spans="2:2">
-      <c r="B189" s="3"/>
-    </row>
-    <row r="190" ht="15.15" spans="2:2">
-      <c r="B190" s="3"/>
-    </row>
-    <row r="191" ht="15.15" spans="2:2">
-      <c r="B191" s="3"/>
-    </row>
-    <row r="192" ht="15.15" spans="2:2">
-      <c r="B192" s="3"/>
-    </row>
-    <row r="193" ht="15.15" spans="2:2">
-      <c r="B193" s="3"/>
-    </row>
-    <row r="194" ht="15.15" spans="2:2">
-      <c r="B194" s="3"/>
+    <row r="150" customFormat="1" spans="1:7">
+      <c r="A150" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" spans="1:7">
+      <c r="A151" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" spans="1:7">
+      <c r="A152" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" spans="1:7">
+      <c r="A153" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" spans="1:7">
+      <c r="A154" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" customFormat="1" spans="1:7">
+      <c r="A155" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G155" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" customFormat="1" spans="1:7">
+      <c r="A156" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" spans="1:7">
+      <c r="A157" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B157" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" customFormat="1" spans="1:7">
+      <c r="A158" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159" customFormat="1" spans="1:7">
+      <c r="A159" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" customFormat="1" spans="1:7">
+      <c r="A160" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B160" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" spans="1:7">
+      <c r="A161" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B161" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" spans="1:7">
+      <c r="A162" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G165" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" ht="28.8" spans="1:7">
+      <c r="A166" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="6"/>
+      <c r="B167" s="10"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+      <c r="G167" s="6"/>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="6"/>
+      <c r="B168" s="10"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="6"/>
+      <c r="E168" s="6"/>
+      <c r="F168" s="6"/>
+      <c r="G168" s="6"/>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" s="6"/>
+      <c r="B169" s="10"/>
+      <c r="C169" s="6"/>
+      <c r="D169" s="6"/>
+      <c r="E169" s="6"/>
+      <c r="F169" s="6"/>
+      <c r="G169" s="6"/>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" s="6"/>
+      <c r="B170" s="10"/>
+      <c r="C170" s="6"/>
+      <c r="D170" s="6"/>
+      <c r="E170" s="6"/>
+      <c r="F170" s="6"/>
+      <c r="G170" s="6"/>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="6"/>
+      <c r="B171" s="10"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="6"/>
+      <c r="E171" s="6"/>
+      <c r="F171" s="6"/>
+      <c r="G171" s="6"/>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="6"/>
+      <c r="B172" s="10"/>
+      <c r="C172" s="6"/>
+      <c r="D172" s="6"/>
+      <c r="E172" s="6"/>
+      <c r="F172" s="6"/>
+      <c r="G172" s="6"/>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" s="6"/>
+      <c r="B173" s="10"/>
+      <c r="C173" s="6"/>
+      <c r="D173" s="6"/>
+      <c r="E173" s="6"/>
+      <c r="F173" s="6"/>
+      <c r="G173" s="6"/>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" s="6"/>
+      <c r="B174" s="10"/>
+      <c r="C174" s="6"/>
+      <c r="D174" s="6"/>
+      <c r="E174" s="6"/>
+      <c r="F174" s="6"/>
+      <c r="G174" s="6"/>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="6"/>
+      <c r="B175" s="10"/>
+      <c r="C175" s="6"/>
+      <c r="D175" s="6"/>
+      <c r="E175" s="6"/>
+      <c r="F175" s="6"/>
+      <c r="G175" s="6"/>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="6"/>
+      <c r="B176" s="10"/>
+      <c r="C176" s="6"/>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
+      <c r="G176" s="6"/>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" s="6"/>
+      <c r="B177" s="10"/>
+      <c r="C177" s="6"/>
+      <c r="D177" s="6"/>
+      <c r="E177" s="6"/>
+      <c r="F177" s="6"/>
+      <c r="G177" s="6"/>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" s="6"/>
+      <c r="B178" s="10"/>
+      <c r="C178" s="6"/>
+      <c r="D178" s="6"/>
+      <c r="E178" s="6"/>
+      <c r="F178" s="6"/>
+      <c r="G178" s="6"/>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" s="6"/>
+      <c r="B179" s="10"/>
+      <c r="C179" s="6"/>
+      <c r="D179" s="6"/>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
+      <c r="G179" s="6"/>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" s="6"/>
+      <c r="B180" s="10"/>
+      <c r="C180" s="6"/>
+      <c r="D180" s="6"/>
+      <c r="E180" s="6"/>
+      <c r="F180" s="6"/>
+      <c r="G180" s="6"/>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" s="6"/>
+      <c r="B181" s="10"/>
+      <c r="C181" s="6"/>
+      <c r="D181" s="6"/>
+      <c r="E181" s="6"/>
+      <c r="F181" s="6"/>
+      <c r="G181" s="6"/>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="6"/>
+      <c r="B182" s="10"/>
+      <c r="C182" s="6"/>
+      <c r="D182" s="6"/>
+      <c r="E182" s="6"/>
+      <c r="F182" s="6"/>
+      <c r="G182" s="6"/>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="6"/>
+      <c r="B183" s="10"/>
+      <c r="C183" s="6"/>
+      <c r="D183" s="6"/>
+      <c r="E183" s="6"/>
+      <c r="F183" s="6"/>
+      <c r="G183" s="6"/>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="6"/>
+      <c r="B184" s="10"/>
+      <c r="C184" s="6"/>
+      <c r="D184" s="6"/>
+      <c r="E184" s="6"/>
+      <c r="F184" s="6"/>
+      <c r="G184" s="6"/>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="6"/>
+      <c r="B185" s="10"/>
+      <c r="C185" s="6"/>
+      <c r="D185" s="6"/>
+      <c r="E185" s="6"/>
+      <c r="F185" s="6"/>
+      <c r="G185" s="6"/>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="6"/>
+      <c r="B186" s="10"/>
+      <c r="C186" s="6"/>
+      <c r="D186" s="6"/>
+      <c r="E186" s="6"/>
+      <c r="F186" s="6"/>
+      <c r="G186" s="6"/>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="6"/>
+      <c r="B187" s="10"/>
+      <c r="C187" s="6"/>
+      <c r="D187" s="6"/>
+      <c r="E187" s="6"/>
+      <c r="F187" s="6"/>
+      <c r="G187" s="6"/>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="6"/>
+      <c r="B188" s="10"/>
+      <c r="C188" s="6"/>
+      <c r="D188" s="6"/>
+      <c r="E188" s="6"/>
+      <c r="F188" s="6"/>
+      <c r="G188" s="6"/>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" s="6"/>
+      <c r="B189" s="10"/>
+      <c r="C189" s="6"/>
+      <c r="D189" s="6"/>
+      <c r="E189" s="6"/>
+      <c r="F189" s="6"/>
+      <c r="G189" s="6"/>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" s="6"/>
+      <c r="B190" s="10"/>
+      <c r="C190" s="6"/>
+      <c r="D190" s="6"/>
+      <c r="E190" s="6"/>
+      <c r="F190" s="6"/>
+      <c r="G190" s="6"/>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="6"/>
+      <c r="B191" s="10"/>
+      <c r="C191" s="6"/>
+      <c r="D191" s="6"/>
+      <c r="E191" s="6"/>
+      <c r="F191" s="6"/>
+      <c r="G191" s="6"/>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="6"/>
+      <c r="B192" s="10"/>
+      <c r="C192" s="6"/>
+      <c r="D192" s="6"/>
+      <c r="E192" s="6"/>
+      <c r="F192" s="6"/>
+      <c r="G192" s="6"/>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="6"/>
+      <c r="B193" s="10"/>
+      <c r="C193" s="6"/>
+      <c r="D193" s="6"/>
+      <c r="E193" s="6"/>
+      <c r="F193" s="6"/>
+      <c r="G193" s="6"/>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="6"/>
+      <c r="B194" s="10"/>
+      <c r="C194" s="6"/>
+      <c r="D194" s="6"/>
+      <c r="E194" s="6"/>
+      <c r="F194" s="6"/>
+      <c r="G194" s="6"/>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="6"/>
+      <c r="B195" s="6"/>
+      <c r="C195" s="6"/>
+      <c r="D195" s="6"/>
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
+      <c r="G195" s="6"/>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="6"/>
+      <c r="B196" s="6"/>
+      <c r="C196" s="6"/>
+      <c r="D196" s="6"/>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6"/>
+      <c r="G196" s="6"/>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="6"/>
+      <c r="B197" s="6"/>
+      <c r="C197" s="6"/>
+      <c r="D197" s="6"/>
+      <c r="E197" s="6"/>
+      <c r="F197" s="6"/>
+      <c r="G197" s="6"/>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="6"/>
+      <c r="B198" s="6"/>
+      <c r="C198" s="6"/>
+      <c r="D198" s="6"/>
+      <c r="E198" s="6"/>
+      <c r="F198" s="6"/>
+      <c r="G198" s="6"/>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="6"/>
+      <c r="B199" s="6"/>
+      <c r="C199" s="6"/>
+      <c r="D199" s="6"/>
+      <c r="E199" s="6"/>
+      <c r="F199" s="6"/>
+      <c r="G199" s="6"/>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="6"/>
+      <c r="B200" s="6"/>
+      <c r="C200" s="6"/>
+      <c r="D200" s="6"/>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6"/>
+      <c r="G200" s="6"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G147" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G165" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -5651,7 +6300,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D806"/>
+  <dimension ref="A1:D821"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="101.666666666667" style="1" customWidth="1"/>
@@ -5662,7 +6311,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -5670,7 +6319,7 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -5678,7 +6327,7 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
@@ -5686,7 +6335,7 @@
     </row>
     <row r="4" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
@@ -5694,7 +6343,7 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B5"/>
       <c r="C5"/>
@@ -5702,7 +6351,7 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B6"/>
       <c r="C6"/>
@@ -5710,7 +6359,7 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B7"/>
       <c r="C7"/>
@@ -5718,7 +6367,7 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -5726,7 +6375,7 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
@@ -5734,7 +6383,7 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -5742,7 +6391,7 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11"/>
       <c r="C11"/>
@@ -5750,7 +6399,7 @@
     </row>
     <row r="12" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -5758,7 +6407,7 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -5766,7 +6415,7 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14"/>
       <c r="C14"/>
@@ -5774,7 +6423,7 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -5782,7 +6431,7 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -5790,7 +6439,7 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -5798,21 +6447,23 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="15.15" spans="1:4">
-      <c r="A19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>182</v>
+        <v>338</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
@@ -5820,7 +6471,7 @@
     </row>
     <row r="21" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>252</v>
+        <v>183</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
@@ -5828,7 +6479,7 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>164</v>
+        <v>253</v>
       </c>
       <c r="B22"/>
       <c r="C22"/>
@@ -5836,7 +6487,7 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>288</v>
+        <v>165</v>
       </c>
       <c r="B23"/>
       <c r="C23"/>
@@ -5844,7 +6495,7 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>258</v>
+        <v>287</v>
       </c>
       <c r="B24"/>
       <c r="C24"/>
@@ -5852,7 +6503,7 @@
     </row>
     <row r="25" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A25" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B25"/>
       <c r="C25"/>
@@ -5860,7 +6511,7 @@
     </row>
     <row r="26" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="B26"/>
       <c r="C26"/>
@@ -5868,7 +6519,7 @@
     </row>
     <row r="27" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A27" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
@@ -5876,7 +6527,7 @@
     </row>
     <row r="28" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B28"/>
       <c r="C28"/>
@@ -5884,7 +6535,7 @@
     </row>
     <row r="29" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A29" s="3" t="s">
-        <v>110</v>
+        <v>279</v>
       </c>
       <c r="B29"/>
       <c r="C29"/>
@@ -5892,7 +6543,7 @@
     </row>
     <row r="30" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>204</v>
+        <v>301</v>
       </c>
       <c r="B30"/>
       <c r="C30"/>
@@ -5900,7 +6551,7 @@
     </row>
     <row r="31" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A31" s="3" t="s">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="B31"/>
       <c r="C31"/>
@@ -5908,7 +6559,7 @@
     </row>
     <row r="32" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="B32"/>
       <c r="C32"/>
@@ -5916,7 +6567,7 @@
     </row>
     <row r="33" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>234</v>
+        <v>305</v>
       </c>
       <c r="B33"/>
       <c r="C33"/>
@@ -5924,7 +6575,7 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="B34"/>
       <c r="C34"/>
@@ -5932,7 +6583,7 @@
     </row>
     <row r="35" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="B35"/>
       <c r="C35"/>
@@ -5940,7 +6591,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B36"/>
       <c r="C36"/>
@@ -5948,7 +6599,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B37"/>
       <c r="C37"/>
@@ -5956,7 +6607,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B38"/>
       <c r="C38"/>
@@ -5964,7 +6615,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
       <c r="B39"/>
       <c r="C39"/>
@@ -5972,98 +6623,128 @@
     </row>
     <row r="40" ht="15.15" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" ht="15.15" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" ht="15.15" spans="1:4">
       <c r="A42" s="3" t="s">
-        <v>8</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" ht="15.15" spans="1:4">
       <c r="A43" s="3" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" ht="15.15" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="45" ht="15.15" spans="1:4">
       <c r="A45" s="3" t="s">
-        <v>102</v>
+        <v>283</v>
       </c>
     </row>
     <row r="46" ht="15.15" spans="1:4">
       <c r="A46" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" ht="15.15" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>192</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" ht="15.15" spans="1:4">
       <c r="A48" s="3" t="s">
-        <v>256</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" ht="15.15" spans="1:1">
       <c r="A49" s="3" t="s">
-        <v>78</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50" ht="15.15" spans="1:1">
-      <c r="A50" s="3"/>
+      <c r="A50" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="51" ht="15.15" spans="1:1">
-      <c r="A51" s="3"/>
+      <c r="A51" s="3" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="52" ht="15.15" spans="1:1">
-      <c r="A52" s="3"/>
+      <c r="A52" s="3" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="53" ht="15.15" spans="1:1">
-      <c r="A53" s="3"/>
+      <c r="A53" s="3" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="54" ht="15.15" spans="1:1">
-      <c r="A54" s="3"/>
+      <c r="A54" s="3" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="55" ht="15.15" spans="1:1">
-      <c r="A55" s="3"/>
+      <c r="A55" s="3" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="56" ht="15.15" spans="1:1">
-      <c r="A56" s="3"/>
+      <c r="A56" s="3" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="57" ht="15.15" spans="1:1">
-      <c r="A57" s="3"/>
+      <c r="A57" s="3" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="58" ht="15.15" spans="1:1">
-      <c r="A58" s="3"/>
+      <c r="A58" s="3" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="59" ht="15.15" spans="1:1">
-      <c r="A59" s="3"/>
+      <c r="A59" s="3" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="60" ht="15.15" spans="1:1">
-      <c r="A60" s="3"/>
+      <c r="A60" s="3" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="61" ht="15.15" spans="1:1">
-      <c r="A61" s="3"/>
+      <c r="A61" s="3" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="62" ht="15.15" spans="1:1">
-      <c r="A62" s="3"/>
+      <c r="A62" s="3" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="63" ht="15.15" spans="1:1">
-      <c r="A63" s="3"/>
+      <c r="A63" s="3" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="64" ht="15.15" spans="1:1">
-      <c r="A64" s="3"/>
+      <c r="A64" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="65" ht="15.15" spans="1:1">
       <c r="A65" s="3"/>
@@ -8290,6 +8971,51 @@
     </row>
     <row r="806" ht="15.15" spans="1:1">
       <c r="A806" s="3"/>
+    </row>
+    <row r="807" ht="15.15" spans="1:1">
+      <c r="A807" s="3"/>
+    </row>
+    <row r="808" ht="15.15" spans="1:1">
+      <c r="A808" s="3"/>
+    </row>
+    <row r="809" ht="15.15" spans="1:1">
+      <c r="A809" s="3"/>
+    </row>
+    <row r="810" ht="15.15" spans="1:1">
+      <c r="A810" s="3"/>
+    </row>
+    <row r="811" ht="15.15" spans="1:1">
+      <c r="A811" s="3"/>
+    </row>
+    <row r="812" ht="15.15" spans="1:1">
+      <c r="A812" s="3"/>
+    </row>
+    <row r="813" ht="15.15" spans="1:1">
+      <c r="A813" s="3"/>
+    </row>
+    <row r="814" ht="15.15" spans="1:1">
+      <c r="A814" s="3"/>
+    </row>
+    <row r="815" ht="15.15" spans="1:1">
+      <c r="A815" s="3"/>
+    </row>
+    <row r="816" ht="15.15" spans="1:1">
+      <c r="A816" s="3"/>
+    </row>
+    <row r="817" ht="15.15" spans="1:1">
+      <c r="A817" s="3"/>
+    </row>
+    <row r="818" ht="15.15" spans="1:1">
+      <c r="A818" s="3"/>
+    </row>
+    <row r="819" ht="15.15" spans="1:1">
+      <c r="A819" s="3"/>
+    </row>
+    <row r="820" ht="15.15" spans="1:1">
+      <c r="A820" s="3"/>
+    </row>
+    <row r="821" ht="15.15" spans="1:1">
+      <c r="A821" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testdata/configurationTST/execute.xlsx
+++ b/testdata/configurationTST/execute.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="21216" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$171</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="353">
   <si>
     <t>App</t>
   </si>
@@ -1039,6 +1039,39 @@
   </si>
   <si>
     <t>C70944</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70945</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70946</t>
+  </si>
+  <si>
+    <t>C70947</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70948</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70949</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70950</t>
   </si>
   <si>
     <t>Automated Test Names</t>
@@ -1786,7 +1819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1813,6 +1846,7 @@
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2151,7 +2185,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
@@ -4133,7 +4167,7 @@
         <v>12</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:7">
@@ -4179,7 +4213,7 @@
         <v>12</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:7">
@@ -4685,7 +4719,7 @@
         <v>12</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:7">
@@ -5053,7 +5087,7 @@
         <v>12</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -5976,314 +6010,605 @@
         <v>13</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
-      <c r="A167" s="6"/>
-      <c r="B167" s="10"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" s="6"/>
-      <c r="B168" s="10"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" s="6"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" s="6"/>
-      <c r="B170" s="10"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" s="6"/>
-      <c r="B171" s="10"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" s="6"/>
-      <c r="B172" s="10"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-    </row>
-    <row r="173" spans="1:7">
+    <row r="167" customFormat="1" spans="1:7">
+      <c r="A167" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G167" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" spans="1:7">
+      <c r="A168" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G168" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" customFormat="1" spans="1:7">
+      <c r="A169" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G169" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" spans="1:7">
+      <c r="A170" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" spans="1:7">
+      <c r="A171" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G171" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" customFormat="1" spans="1:7">
+      <c r="A172" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G172" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173" customFormat="1" spans="1:7">
       <c r="A173" s="6"/>
-      <c r="B173" s="10"/>
+      <c r="B173" s="6"/>
       <c r="C173" s="6"/>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
+      <c r="F173" s="8"/>
       <c r="G173" s="6"/>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" customFormat="1" spans="1:7">
       <c r="A174" s="6"/>
-      <c r="B174" s="10"/>
+      <c r="B174" s="6"/>
       <c r="C174" s="6"/>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
+      <c r="F174" s="8"/>
       <c r="G174" s="6"/>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" customFormat="1" spans="1:7">
       <c r="A175" s="6"/>
-      <c r="B175" s="10"/>
+      <c r="B175" s="6"/>
       <c r="C175" s="6"/>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
+      <c r="F175" s="8"/>
       <c r="G175" s="6"/>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" customFormat="1" spans="1:7">
       <c r="A176" s="6"/>
-      <c r="B176" s="10"/>
+      <c r="B176" s="6"/>
       <c r="C176" s="6"/>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
+      <c r="F176" s="8"/>
       <c r="G176" s="6"/>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" customFormat="1" spans="1:7">
       <c r="A177" s="6"/>
-      <c r="B177" s="10"/>
+      <c r="B177" s="6"/>
       <c r="C177" s="6"/>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
+      <c r="F177" s="8"/>
       <c r="G177" s="6"/>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" customFormat="1" spans="1:7">
       <c r="A178" s="6"/>
-      <c r="B178" s="10"/>
+      <c r="B178" s="6"/>
       <c r="C178" s="6"/>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
+      <c r="F178" s="8"/>
       <c r="G178" s="6"/>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" customFormat="1" spans="1:7">
       <c r="A179" s="6"/>
-      <c r="B179" s="10"/>
+      <c r="B179" s="6"/>
       <c r="C179" s="6"/>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
+      <c r="F179" s="8"/>
       <c r="G179" s="6"/>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" customFormat="1" spans="1:7">
       <c r="A180" s="6"/>
-      <c r="B180" s="10"/>
+      <c r="B180" s="6"/>
       <c r="C180" s="6"/>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
+      <c r="F180" s="8"/>
       <c r="G180" s="6"/>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" customFormat="1" spans="1:7">
       <c r="A181" s="6"/>
-      <c r="B181" s="10"/>
+      <c r="B181" s="6"/>
       <c r="C181" s="6"/>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
+      <c r="F181" s="8"/>
       <c r="G181" s="6"/>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" customFormat="1" spans="1:7">
       <c r="A182" s="6"/>
-      <c r="B182" s="10"/>
+      <c r="B182" s="6"/>
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
+      <c r="F182" s="8"/>
       <c r="G182" s="6"/>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" customFormat="1" spans="1:7">
       <c r="A183" s="6"/>
-      <c r="B183" s="10"/>
+      <c r="B183" s="6"/>
       <c r="C183" s="6"/>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
+      <c r="F183" s="8"/>
       <c r="G183" s="6"/>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" customFormat="1" spans="1:7">
       <c r="A184" s="6"/>
-      <c r="B184" s="10"/>
+      <c r="B184" s="6"/>
       <c r="C184" s="6"/>
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
+      <c r="F184" s="8"/>
       <c r="G184" s="6"/>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" customFormat="1" spans="1:7">
       <c r="A185" s="6"/>
-      <c r="B185" s="10"/>
+      <c r="B185" s="6"/>
       <c r="C185" s="6"/>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
+      <c r="F185" s="8"/>
       <c r="G185" s="6"/>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" customFormat="1" spans="1:7">
       <c r="A186" s="6"/>
-      <c r="B186" s="10"/>
+      <c r="B186" s="6"/>
       <c r="C186" s="6"/>
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
+      <c r="F186" s="8"/>
       <c r="G186" s="6"/>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" customFormat="1" spans="1:7">
       <c r="A187" s="6"/>
-      <c r="B187" s="10"/>
+      <c r="B187" s="6"/>
       <c r="C187" s="6"/>
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
+      <c r="F187" s="8"/>
       <c r="G187" s="6"/>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" customFormat="1" spans="1:7">
       <c r="A188" s="6"/>
-      <c r="B188" s="10"/>
+      <c r="B188" s="6"/>
       <c r="C188" s="6"/>
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
+      <c r="F188" s="8"/>
       <c r="G188" s="6"/>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" customFormat="1" spans="1:7">
       <c r="A189" s="6"/>
-      <c r="B189" s="10"/>
+      <c r="B189" s="6"/>
       <c r="C189" s="6"/>
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
+      <c r="F189" s="8"/>
       <c r="G189" s="6"/>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" customFormat="1" spans="1:7">
       <c r="A190" s="6"/>
-      <c r="B190" s="10"/>
+      <c r="B190" s="6"/>
       <c r="C190" s="6"/>
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
+      <c r="F190" s="8"/>
       <c r="G190" s="6"/>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" customFormat="1" spans="1:7">
       <c r="A191" s="6"/>
-      <c r="B191" s="10"/>
+      <c r="B191" s="6"/>
       <c r="C191" s="6"/>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
+      <c r="F191" s="8"/>
       <c r="G191" s="6"/>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" customFormat="1" spans="1:7">
       <c r="A192" s="6"/>
-      <c r="B192" s="10"/>
+      <c r="B192" s="6"/>
       <c r="C192" s="6"/>
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
+      <c r="F192" s="8"/>
       <c r="G192" s="6"/>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" customFormat="1" spans="1:7">
       <c r="A193" s="6"/>
-      <c r="B193" s="10"/>
+      <c r="B193" s="6"/>
       <c r="C193" s="6"/>
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
+      <c r="F193" s="8"/>
       <c r="G193" s="6"/>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" customFormat="1" spans="1:7">
       <c r="A194" s="6"/>
-      <c r="B194" s="10"/>
+      <c r="B194" s="6"/>
       <c r="C194" s="6"/>
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
+      <c r="F194" s="8"/>
       <c r="G194" s="6"/>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" customFormat="1" spans="1:7">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
+      <c r="F195" s="8"/>
       <c r="G195" s="6"/>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" customFormat="1" spans="1:7">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
+      <c r="F196" s="8"/>
       <c r="G196" s="6"/>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" customFormat="1" spans="1:7">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
+      <c r="F197" s="8"/>
       <c r="G197" s="6"/>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" customFormat="1" spans="1:7">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
+      <c r="F198" s="8"/>
       <c r="G198" s="6"/>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" customFormat="1" spans="1:7">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
+      <c r="F199" s="8"/>
       <c r="G199" s="6"/>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" customFormat="1" spans="1:7">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
+      <c r="F200" s="8"/>
       <c r="G200" s="6"/>
     </row>
+    <row r="201" customFormat="1" spans="1:7">
+      <c r="A201" s="6"/>
+      <c r="B201" s="6"/>
+      <c r="C201" s="6"/>
+      <c r="D201" s="6"/>
+      <c r="E201" s="6"/>
+      <c r="F201" s="8"/>
+      <c r="G201" s="6"/>
+    </row>
+    <row r="202" customFormat="1" spans="1:7">
+      <c r="A202" s="6"/>
+      <c r="B202" s="6"/>
+      <c r="C202" s="6"/>
+      <c r="D202" s="6"/>
+      <c r="E202" s="6"/>
+      <c r="F202" s="8"/>
+      <c r="G202" s="6"/>
+    </row>
+    <row r="203" customFormat="1" spans="1:7">
+      <c r="A203" s="6"/>
+      <c r="B203" s="6"/>
+      <c r="C203" s="6"/>
+      <c r="D203" s="6"/>
+      <c r="E203" s="6"/>
+      <c r="F203" s="8"/>
+      <c r="G203" s="6"/>
+    </row>
+    <row r="204" customFormat="1" spans="1:7">
+      <c r="A204" s="6"/>
+      <c r="B204" s="6"/>
+      <c r="C204" s="6"/>
+      <c r="D204" s="6"/>
+      <c r="E204" s="6"/>
+      <c r="F204" s="8"/>
+      <c r="G204" s="6"/>
+    </row>
+    <row r="205" customFormat="1" spans="1:7">
+      <c r="A205" s="6"/>
+      <c r="B205" s="6"/>
+      <c r="C205" s="6"/>
+      <c r="D205" s="6"/>
+      <c r="E205" s="6"/>
+      <c r="F205" s="8"/>
+      <c r="G205" s="6"/>
+    </row>
+    <row r="206" customFormat="1" spans="1:7">
+      <c r="A206" s="6"/>
+      <c r="B206" s="6"/>
+      <c r="C206" s="6"/>
+      <c r="D206" s="6"/>
+      <c r="E206" s="6"/>
+      <c r="F206" s="8"/>
+      <c r="G206" s="6"/>
+    </row>
+    <row r="207" customFormat="1" spans="1:7">
+      <c r="A207" s="6"/>
+      <c r="B207" s="6"/>
+      <c r="C207" s="6"/>
+      <c r="D207" s="6"/>
+      <c r="E207" s="6"/>
+      <c r="F207" s="8"/>
+      <c r="G207" s="6"/>
+    </row>
+    <row r="208" customFormat="1" spans="1:7">
+      <c r="A208" s="6"/>
+      <c r="B208" s="6"/>
+      <c r="C208" s="6"/>
+      <c r="D208" s="6"/>
+      <c r="E208" s="6"/>
+      <c r="F208" s="8"/>
+      <c r="G208" s="6"/>
+    </row>
+    <row r="209" customFormat="1" spans="1:7">
+      <c r="A209" s="6"/>
+      <c r="B209" s="6"/>
+      <c r="C209" s="6"/>
+      <c r="D209" s="6"/>
+      <c r="E209" s="6"/>
+      <c r="F209" s="8"/>
+      <c r="G209" s="6"/>
+    </row>
+    <row r="210" customFormat="1" spans="1:7">
+      <c r="A210" s="6"/>
+      <c r="B210" s="6"/>
+      <c r="C210" s="6"/>
+      <c r="D210" s="6"/>
+      <c r="E210" s="6"/>
+      <c r="F210" s="8"/>
+      <c r="G210" s="6"/>
+    </row>
+    <row r="211" customFormat="1" spans="1:7">
+      <c r="A211" s="6"/>
+      <c r="B211" s="6"/>
+      <c r="C211" s="6"/>
+      <c r="D211" s="6"/>
+      <c r="E211" s="6"/>
+      <c r="F211" s="8"/>
+      <c r="G211" s="6"/>
+    </row>
+    <row r="212" customFormat="1" spans="1:7">
+      <c r="A212" s="6"/>
+      <c r="B212" s="6"/>
+      <c r="C212" s="6"/>
+      <c r="D212" s="6"/>
+      <c r="E212" s="6"/>
+      <c r="F212" s="8"/>
+      <c r="G212" s="6"/>
+    </row>
+    <row r="213" customFormat="1" spans="1:7">
+      <c r="A213" s="6"/>
+      <c r="B213" s="6"/>
+      <c r="C213" s="6"/>
+      <c r="D213" s="6"/>
+      <c r="E213" s="6"/>
+      <c r="F213" s="8"/>
+      <c r="G213" s="6"/>
+    </row>
+    <row r="214" customFormat="1" spans="1:7">
+      <c r="A214" s="6"/>
+      <c r="B214" s="6"/>
+      <c r="C214" s="6"/>
+      <c r="D214" s="6"/>
+      <c r="E214" s="6"/>
+      <c r="F214" s="8"/>
+      <c r="G214" s="6"/>
+    </row>
+    <row r="215" customFormat="1" spans="1:7">
+      <c r="A215" s="6"/>
+      <c r="B215" s="6"/>
+      <c r="C215" s="6"/>
+      <c r="D215" s="6"/>
+      <c r="E215" s="6"/>
+      <c r="F215" s="8"/>
+      <c r="G215" s="6"/>
+    </row>
+    <row r="216" customFormat="1" spans="1:7">
+      <c r="A216" s="6"/>
+      <c r="B216" s="6"/>
+      <c r="C216" s="6"/>
+      <c r="D216" s="6"/>
+      <c r="E216" s="6"/>
+      <c r="F216" s="8"/>
+      <c r="G216" s="6"/>
+    </row>
+    <row r="217" customFormat="1" spans="1:7">
+      <c r="A217" s="6"/>
+      <c r="B217" s="6"/>
+      <c r="C217" s="6"/>
+      <c r="D217" s="6"/>
+      <c r="E217" s="6"/>
+      <c r="F217" s="8"/>
+      <c r="G217" s="6"/>
+    </row>
+    <row r="218" customFormat="1" spans="1:7">
+      <c r="A218" s="6"/>
+      <c r="B218" s="6"/>
+      <c r="C218" s="6"/>
+      <c r="D218" s="6"/>
+      <c r="E218" s="6"/>
+      <c r="F218" s="8"/>
+      <c r="G218" s="6"/>
+    </row>
+    <row r="219" customFormat="1" spans="1:7">
+      <c r="A219" s="6"/>
+      <c r="B219" s="6"/>
+      <c r="C219" s="6"/>
+      <c r="D219" s="6"/>
+      <c r="E219" s="6"/>
+      <c r="F219" s="8"/>
+      <c r="G219" s="6"/>
+    </row>
+    <row r="220" customFormat="1" spans="1:7">
+      <c r="A220" s="6"/>
+      <c r="B220" s="6"/>
+      <c r="C220" s="6"/>
+      <c r="D220" s="6"/>
+      <c r="E220" s="6"/>
+      <c r="F220" s="8"/>
+      <c r="G220" s="6"/>
+    </row>
+    <row r="221" customFormat="1" spans="1:7">
+      <c r="A221" s="6"/>
+      <c r="B221" s="6"/>
+      <c r="C221" s="6"/>
+      <c r="D221" s="6"/>
+      <c r="E221" s="6"/>
+      <c r="F221" s="8"/>
+      <c r="G221" s="6"/>
+    </row>
+    <row r="222" customFormat="1" spans="1:7">
+      <c r="A222" s="6"/>
+      <c r="B222" s="6"/>
+      <c r="C222" s="6"/>
+      <c r="D222" s="6"/>
+      <c r="E222" s="6"/>
+      <c r="F222" s="8"/>
+      <c r="G222" s="6"/>
+    </row>
+    <row r="223" customFormat="1" spans="1:7">
+      <c r="A223" s="6"/>
+      <c r="B223" s="6"/>
+      <c r="C223" s="6"/>
+      <c r="D223" s="6"/>
+      <c r="E223" s="6"/>
+      <c r="F223" s="8"/>
+      <c r="G223" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G165" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G171" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -6311,7 +6636,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6447,7 +6772,7 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
@@ -6463,7 +6788,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
@@ -6575,7 +6900,7 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B34"/>
       <c r="C34"/>
@@ -6658,7 +6983,7 @@
     </row>
     <row r="47" ht="15.15" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" ht="15.15" spans="1:4">
@@ -6698,7 +7023,7 @@
     </row>
     <row r="55" ht="15.15" spans="1:1">
       <c r="A55" s="3" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56" ht="15.15" spans="1:1">

--- a/testdata/configurationTST/execute.xlsx
+++ b/testdata/configurationTST/execute.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21216" windowHeight="8964"/>
+    <workbookView windowWidth="28800" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$186</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="380">
   <si>
     <t>App</t>
   </si>
@@ -81,21 +81,21 @@
     <t>C70780</t>
   </si>
   <si>
+    <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70781</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70782</t>
+  </si>
+  <si>
     <t>off</t>
   </si>
   <si>
-    <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70781</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70782</t>
-  </si>
-  <si>
     <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_6</t>
   </si>
   <si>
@@ -1074,6 +1074,90 @@
     <t>C70950</t>
   </si>
   <si>
+    <t>Authentication_Mobile_Login_Forgot_PIN_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70951</t>
+  </si>
+  <si>
+    <t>Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70952</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70953</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70954</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70955</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70956</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_Multiple_Filter_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70957</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Search_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70958</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Filter_By_Date_Predefined_Date_Range_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70959</t>
+  </si>
+  <si>
+    <t>Loan_Accounts_Header_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70960</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_Input_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70961</t>
+  </si>
+  <si>
+    <t>Manage_Products_Favorite_account_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70962</t>
+  </si>
+  <si>
+    <t>Manage_Products_Favorite_account_[MOB_ANDROID]-Removal_Of_The_Favorite_Account</t>
+  </si>
+  <si>
+    <t>C70963</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter-Filter_By_Status_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70964</t>
+  </si>
+  <si>
     <t>Automated Test Names</t>
   </si>
   <si>
@@ -1084,9 +1168,6 @@
   </si>
   <si>
     <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[MOB_ANDROID]</t>
   </si>
   <si>
     <t>Manage_Products_Nickname_Product_[MOB_ANDROID]</t>
@@ -1819,7 +1900,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1846,7 +1927,11 @@
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2258,7 +2343,7 @@
         <v>12</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:7">
@@ -2266,10 +2351,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>10</v>
@@ -2289,22 +2374,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
@@ -2327,7 +2412,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -2350,7 +2435,7 @@
         <v>12</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -2373,7 +2458,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:7">
@@ -2396,7 +2481,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:7">
@@ -2419,7 +2504,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:7">
@@ -2442,7 +2527,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:7">
@@ -2465,7 +2550,7 @@
         <v>12</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:7">
@@ -2488,7 +2573,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:7">
@@ -2511,7 +2596,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:7">
@@ -2534,7 +2619,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:7">
@@ -2557,7 +2642,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:7">
@@ -2580,7 +2665,7 @@
         <v>12</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:7">
@@ -2603,7 +2688,7 @@
         <v>12</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:7">
@@ -2626,7 +2711,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:7">
@@ -2649,7 +2734,7 @@
         <v>12</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:7">
@@ -2672,7 +2757,7 @@
         <v>12</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:7">
@@ -2695,7 +2780,7 @@
         <v>12</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:7">
@@ -2718,7 +2803,7 @@
         <v>12</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:7">
@@ -2741,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:7">
@@ -2764,7 +2849,7 @@
         <v>12</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:7">
@@ -2787,7 +2872,7 @@
         <v>12</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:7">
@@ -2810,7 +2895,7 @@
         <v>12</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:7">
@@ -2833,7 +2918,7 @@
         <v>12</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:7">
@@ -2856,7 +2941,7 @@
         <v>12</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:7">
@@ -2879,7 +2964,7 @@
         <v>12</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:7">
@@ -2902,7 +2987,7 @@
         <v>12</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:7">
@@ -2925,7 +3010,7 @@
         <v>12</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:7">
@@ -2971,7 +3056,7 @@
         <v>12</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:7">
@@ -3017,7 +3102,7 @@
         <v>12</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:7">
@@ -3040,7 +3125,7 @@
         <v>12</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:7">
@@ -3086,7 +3171,7 @@
         <v>12</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:7">
@@ -3132,7 +3217,7 @@
         <v>12</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
@@ -3155,7 +3240,7 @@
         <v>12</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:7">
@@ -3178,7 +3263,7 @@
         <v>12</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:7">
@@ -3201,7 +3286,7 @@
         <v>12</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:7">
@@ -3224,7 +3309,7 @@
         <v>12</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:7">
@@ -3247,7 +3332,7 @@
         <v>12</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:7">
@@ -3293,7 +3378,7 @@
         <v>12</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:7">
@@ -3316,7 +3401,7 @@
         <v>12</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:7">
@@ -3339,7 +3424,7 @@
         <v>12</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:7">
@@ -3385,7 +3470,7 @@
         <v>12</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:7">
@@ -3408,7 +3493,7 @@
         <v>12</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -3431,7 +3516,7 @@
         <v>12</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -3454,7 +3539,7 @@
         <v>12</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:7">
@@ -3500,7 +3585,7 @@
         <v>12</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:7">
@@ -3523,7 +3608,7 @@
         <v>12</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:7">
@@ -3546,7 +3631,7 @@
         <v>12</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -3569,7 +3654,7 @@
         <v>12</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:7">
@@ -3592,7 +3677,7 @@
         <v>12</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:7">
@@ -3615,7 +3700,7 @@
         <v>12</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:7">
@@ -3638,7 +3723,7 @@
         <v>12</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:7">
@@ -3661,7 +3746,7 @@
         <v>12</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:7">
@@ -3684,7 +3769,7 @@
         <v>12</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:7">
@@ -3707,7 +3792,7 @@
         <v>12</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:7">
@@ -3730,7 +3815,7 @@
         <v>12</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:7">
@@ -3753,7 +3838,7 @@
         <v>12</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:7">
@@ -3776,7 +3861,7 @@
         <v>12</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -3799,7 +3884,7 @@
         <v>12</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:7">
@@ -3868,7 +3953,7 @@
         <v>12</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:7">
@@ -3891,7 +3976,7 @@
         <v>12</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:7">
@@ -3914,7 +3999,7 @@
         <v>12</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:7">
@@ -3937,7 +4022,7 @@
         <v>12</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:7">
@@ -3960,7 +4045,7 @@
         <v>12</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:7">
@@ -4006,7 +4091,7 @@
         <v>12</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:7">
@@ -4052,7 +4137,7 @@
         <v>12</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:7">
@@ -4075,7 +4160,7 @@
         <v>12</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -4098,7 +4183,7 @@
         <v>12</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -4121,7 +4206,7 @@
         <v>12</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:7">
@@ -4236,7 +4321,7 @@
         <v>12</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:7">
@@ -4259,7 +4344,7 @@
         <v>12</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:7">
@@ -4328,7 +4413,7 @@
         <v>12</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -4351,7 +4436,7 @@
         <v>12</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:7">
@@ -4374,7 +4459,7 @@
         <v>12</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:7">
@@ -4397,7 +4482,7 @@
         <v>12</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:7">
@@ -4420,7 +4505,7 @@
         <v>12</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:7">
@@ -4466,7 +4551,7 @@
         <v>12</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:7">
@@ -4512,7 +4597,7 @@
         <v>12</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:7">
@@ -4535,7 +4620,7 @@
         <v>12</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:7">
@@ -4558,7 +4643,7 @@
         <v>12</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:7">
@@ -4581,7 +4666,7 @@
         <v>12</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -4604,7 +4689,7 @@
         <v>12</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:7">
@@ -4627,7 +4712,7 @@
         <v>12</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:7">
@@ -4650,7 +4735,7 @@
         <v>12</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:7">
@@ -4673,7 +4758,7 @@
         <v>12</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:7">
@@ -4949,7 +5034,7 @@
         <v>12</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:7">
@@ -4972,7 +5057,7 @@
         <v>12</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:7">
@@ -6000,7 +6085,7 @@
       <c r="D166" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E166" s="7" t="s">
+      <c r="E166" s="14" t="s">
         <v>11</v>
       </c>
       <c r="F166" s="6" t="s">
@@ -6029,7 +6114,7 @@
       <c r="F167" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G167" s="14" t="s">
+      <c r="G167" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6052,7 +6137,7 @@
       <c r="F168" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G168" s="14" t="s">
+      <c r="G168" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6075,7 +6160,7 @@
       <c r="F169" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G169" s="14" t="s">
+      <c r="G169" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6098,7 +6183,7 @@
       <c r="F170" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G170" s="14" t="s">
+      <c r="G170" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6121,7 +6206,7 @@
       <c r="F171" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G171" s="14" t="s">
+      <c r="G171" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6144,135 +6229,331 @@
       <c r="F172" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G172" s="14" t="s">
+      <c r="G172" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:7">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="8"/>
-      <c r="G173" s="6"/>
+      <c r="A173" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G173" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="174" customFormat="1" spans="1:7">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="8"/>
-      <c r="G174" s="6"/>
+      <c r="A174" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="175" customFormat="1" spans="1:7">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="8"/>
-      <c r="G175" s="6"/>
+      <c r="A175" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" customFormat="1" spans="1:7">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="8"/>
-      <c r="G176" s="6"/>
+      <c r="A176" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G176" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="177" customFormat="1" spans="1:7">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="6"/>
+      <c r="A177" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G177" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="178" customFormat="1" spans="1:7">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="6"/>
+      <c r="A178" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="179" customFormat="1" spans="1:7">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="8"/>
-      <c r="G179" s="6"/>
+      <c r="A179" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B179" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G179" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="180" customFormat="1" spans="1:7">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="8"/>
-      <c r="G180" s="6"/>
+      <c r="A180" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B180" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G180" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="181" customFormat="1" spans="1:7">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="8"/>
-      <c r="G181" s="6"/>
+      <c r="A181" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G181" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="182" customFormat="1" spans="1:7">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="8"/>
-      <c r="G182" s="6"/>
+      <c r="A182" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G182" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="183" customFormat="1" spans="1:7">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="8"/>
-      <c r="G183" s="6"/>
+      <c r="A183" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G183" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="184" customFormat="1" spans="1:7">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="8"/>
-      <c r="G184" s="6"/>
+      <c r="A184" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G184" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="185" customFormat="1" spans="1:7">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="8"/>
-      <c r="G185" s="6"/>
+      <c r="A185" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G185" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="186" customFormat="1" spans="1:7">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="8"/>
-      <c r="G186" s="6"/>
+      <c r="A186" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G186" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" customFormat="1" spans="1:7">
       <c r="A187" s="6"/>
@@ -6608,7 +6889,7 @@
       <c r="G223" s="6"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G171" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G186" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -6636,7 +6917,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6644,7 +6925,7 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -6772,7 +7053,7 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
@@ -6788,7 +7069,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
@@ -6900,7 +7181,7 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="B34"/>
       <c r="C34"/>
@@ -6983,7 +7264,7 @@
     </row>
     <row r="47" ht="15.15" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" ht="15.15" spans="1:4">
@@ -7023,7 +7304,7 @@
     </row>
     <row r="55" ht="15.15" spans="1:1">
       <c r="A55" s="3" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
     </row>
     <row r="56" ht="15.15" spans="1:1">
